--- a/results/components/gene_names/p4s4.xlsx
+++ b/results/components/gene_names/p4s4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="317">
   <si>
     <t>gene1</t>
   </si>
@@ -22,901 +22,949 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>sli</t>
+  </si>
+  <si>
+    <t>sax</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>asf1</t>
+  </si>
+  <si>
+    <t>cin</t>
+  </si>
+  <si>
+    <t>Tak1</t>
+  </si>
+  <si>
+    <t>Tm1</t>
+  </si>
+  <si>
+    <t>inaC</t>
+  </si>
+  <si>
+    <t>sll</t>
+  </si>
+  <si>
+    <t>Sry-delta</t>
+  </si>
+  <si>
+    <t>capu</t>
+  </si>
+  <si>
+    <t>Msp-300</t>
+  </si>
+  <si>
+    <t>Ddx1</t>
+  </si>
+  <si>
+    <t>Nrx-IV</t>
+  </si>
+  <si>
+    <t>tkv</t>
+  </si>
+  <si>
+    <t>oaf</t>
+  </si>
+  <si>
+    <t>esg</t>
+  </si>
+  <si>
+    <t>apt</t>
+  </si>
+  <si>
+    <t>cas</t>
+  </si>
+  <si>
+    <t>Nrt</t>
+  </si>
+  <si>
+    <t>dock</t>
+  </si>
+  <si>
+    <t>yrt</t>
+  </si>
+  <si>
+    <t>kis</t>
+  </si>
+  <si>
+    <t>osa</t>
+  </si>
+  <si>
+    <t>pbl</t>
+  </si>
+  <si>
+    <t>Hmgs</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>Rab7</t>
+  </si>
+  <si>
+    <t>mri</t>
+  </si>
+  <si>
+    <t>ash2</t>
+  </si>
+  <si>
+    <t>pav</t>
+  </si>
+  <si>
+    <t>qm</t>
+  </si>
+  <si>
+    <t>Mhc</t>
+  </si>
+  <si>
+    <t>dl</t>
+  </si>
+  <si>
+    <t>l(3)mbt</t>
+  </si>
+  <si>
+    <t>Alk</t>
+  </si>
+  <si>
+    <t>fs(2)ltoPP43</t>
+  </si>
+  <si>
+    <t>mfas</t>
+  </si>
+  <si>
+    <t>ksr</t>
+  </si>
+  <si>
+    <t>Tl</t>
+  </si>
+  <si>
+    <t>CG9104</t>
+  </si>
+  <si>
+    <t>jing</t>
+  </si>
+  <si>
+    <t>bt</t>
+  </si>
+  <si>
+    <t>Oseg1</t>
+  </si>
+  <si>
+    <t>Krn</t>
+  </si>
+  <si>
+    <t>sbb</t>
+  </si>
+  <si>
+    <t>hyx</t>
+  </si>
+  <si>
+    <t>CG18369</t>
+  </si>
+  <si>
+    <t>l(2)efl</t>
+  </si>
+  <si>
+    <t>Abl</t>
+  </si>
+  <si>
+    <t>rdx</t>
+  </si>
+  <si>
+    <t>Pka-C3</t>
+  </si>
+  <si>
+    <t>p53</t>
+  </si>
+  <si>
+    <t>Cp1</t>
+  </si>
+  <si>
+    <t>Aph-4</t>
+  </si>
+  <si>
+    <t>Cka</t>
+  </si>
+  <si>
+    <t>bs</t>
+  </si>
+  <si>
+    <t>Khc</t>
+  </si>
+  <si>
+    <t>alph</t>
+  </si>
+  <si>
+    <t>CG9445</t>
+  </si>
+  <si>
+    <t>kuk</t>
+  </si>
+  <si>
+    <t>CtBP</t>
+  </si>
+  <si>
+    <t>cos</t>
+  </si>
+  <si>
+    <t>rad50</t>
+  </si>
+  <si>
+    <t>ppan</t>
+  </si>
+  <si>
+    <t>mus304</t>
+  </si>
+  <si>
+    <t>ex</t>
+  </si>
+  <si>
+    <t>bowl</t>
+  </si>
+  <si>
+    <t>Ank2</t>
+  </si>
+  <si>
+    <t>Syb</t>
+  </si>
+  <si>
+    <t>LCBP1</t>
+  </si>
+  <si>
+    <t>CG2678</t>
+  </si>
+  <si>
+    <t>Idgf4</t>
+  </si>
+  <si>
+    <t>Sxl</t>
+  </si>
+  <si>
+    <t>pdm2</t>
+  </si>
+  <si>
+    <t>lola</t>
+  </si>
+  <si>
+    <t>Mef2</t>
+  </si>
+  <si>
+    <t>bcd</t>
+  </si>
+  <si>
+    <t>bun</t>
+  </si>
+  <si>
+    <t>beta4GalNAcTA</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>dib</t>
+  </si>
+  <si>
+    <t>Apc</t>
+  </si>
+  <si>
+    <t>Vhl</t>
+  </si>
+  <si>
+    <t>dsf</t>
+  </si>
+  <si>
+    <t>Rab5</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>dco</t>
+  </si>
+  <si>
+    <t>LIMK1</t>
+  </si>
+  <si>
+    <t>Pcaf</t>
+  </si>
+  <si>
+    <t>betaTub56D</t>
+  </si>
+  <si>
+    <t>Mlc1</t>
+  </si>
+  <si>
+    <t>CG1942</t>
+  </si>
+  <si>
+    <t>Fas3</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>Cip4</t>
+  </si>
+  <si>
+    <t>ey</t>
+  </si>
+  <si>
+    <t>rux</t>
+  </si>
+  <si>
+    <t>Myo61F</t>
+  </si>
+  <si>
+    <t>jar</t>
+  </si>
+  <si>
+    <t>lic</t>
+  </si>
+  <si>
+    <t>l(1)G0289</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>Ptpmeg</t>
+  </si>
+  <si>
+    <t>Idgf5</t>
+  </si>
+  <si>
+    <t>Arc42</t>
+  </si>
+  <si>
+    <t>Myo31DF</t>
+  </si>
+  <si>
+    <t>Iswi</t>
+  </si>
+  <si>
+    <t>sqd</t>
+  </si>
+  <si>
+    <t>CG17739</t>
+  </si>
+  <si>
+    <t>cbt</t>
+  </si>
+  <si>
+    <t>Dhc64C</t>
+  </si>
+  <si>
+    <t>tup</t>
+  </si>
+  <si>
+    <t>ImpE3</t>
+  </si>
+  <si>
+    <t>CG13850</t>
+  </si>
+  <si>
+    <t>eve</t>
+  </si>
+  <si>
+    <t>drk</t>
+  </si>
+  <si>
+    <t>Dcp-1</t>
+  </si>
+  <si>
+    <t>xl6</t>
+  </si>
+  <si>
+    <t>sina</t>
+  </si>
+  <si>
+    <t>sktl</t>
+  </si>
+  <si>
+    <t>CG10641</t>
+  </si>
+  <si>
+    <t>Dap160</t>
+  </si>
+  <si>
+    <t>crc</t>
+  </si>
+  <si>
+    <t>eIF-4E</t>
+  </si>
+  <si>
+    <t>knrl</t>
+  </si>
+  <si>
+    <t>emb</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Fmr1</t>
+  </si>
+  <si>
+    <t>lilli</t>
+  </si>
+  <si>
+    <t>Su(var)2-10</t>
   </si>
   <si>
     <t>Lis-1</t>
   </si>
   <si>
-    <t>shn</t>
+    <t>tow</t>
+  </si>
+  <si>
+    <t>uzip</t>
+  </si>
+  <si>
+    <t>Crk</t>
+  </si>
+  <si>
+    <t>tamo</t>
+  </si>
+  <si>
+    <t>Bap60</t>
+  </si>
+  <si>
+    <t>E2f2</t>
+  </si>
+  <si>
+    <t>Dscam</t>
+  </si>
+  <si>
+    <t>E2f</t>
+  </si>
+  <si>
+    <t>RhoGAP68F</t>
+  </si>
+  <si>
+    <t>lva</t>
+  </si>
+  <si>
+    <t>emc</t>
+  </si>
+  <si>
+    <t>poe</t>
+  </si>
+  <si>
+    <t>Eip71CD</t>
+  </si>
+  <si>
+    <t>sav</t>
+  </si>
+  <si>
+    <t>CG6416</t>
+  </si>
+  <si>
+    <t>Eip63F-1</t>
+  </si>
+  <si>
+    <t>mbt</t>
+  </si>
+  <si>
+    <t>qkr58E-3</t>
+  </si>
+  <si>
+    <t>stumps</t>
+  </si>
+  <si>
+    <t>mam</t>
+  </si>
+  <si>
+    <t>CG8216</t>
+  </si>
+  <si>
+    <t>ssh</t>
+  </si>
+  <si>
+    <t>Abd-B</t>
+  </si>
+  <si>
+    <t>CycB</t>
+  </si>
+  <si>
+    <t>neur</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>Hr46</t>
+  </si>
+  <si>
+    <t>scrib</t>
+  </si>
+  <si>
+    <t>klar</t>
+  </si>
+  <si>
+    <t>svr</t>
+  </si>
+  <si>
+    <t>chif</t>
+  </si>
+  <si>
+    <t>NetB</t>
+  </si>
+  <si>
+    <t>gro</t>
+  </si>
+  <si>
+    <t>CG34450</t>
+  </si>
+  <si>
+    <t>shg</t>
+  </si>
+  <si>
+    <t>sn</t>
+  </si>
+  <si>
+    <t>tou</t>
+  </si>
+  <si>
+    <t>rg</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>twf</t>
+  </si>
+  <si>
+    <t>noc</t>
+  </si>
+  <si>
+    <t>MYPT-75D</t>
+  </si>
+  <si>
+    <t>raw</t>
+  </si>
+  <si>
+    <t>CG9769</t>
+  </si>
+  <si>
+    <t>phyl</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>Pi3K92E</t>
+  </si>
+  <si>
+    <t>Trl</t>
+  </si>
+  <si>
+    <t>ct</t>
+  </si>
+  <si>
+    <t>drm</t>
+  </si>
+  <si>
+    <t>dpn</t>
+  </si>
+  <si>
+    <t>ash1</t>
+  </si>
+  <si>
+    <t>chinmo</t>
+  </si>
+  <si>
+    <t>flfl</t>
+  </si>
+  <si>
+    <t>spir</t>
+  </si>
+  <si>
+    <t>tra</t>
+  </si>
+  <si>
+    <t>Rpd3</t>
+  </si>
+  <si>
+    <t>kuz</t>
+  </si>
+  <si>
+    <t>fl(2)d</t>
+  </si>
+  <si>
+    <t>form3</t>
+  </si>
+  <si>
+    <t>pcm</t>
+  </si>
+  <si>
+    <t>Cct1</t>
+  </si>
+  <si>
+    <t>tok</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>loco</t>
+  </si>
+  <si>
+    <t>Mitf</t>
+  </si>
+  <si>
+    <t>yellow-f</t>
+  </si>
+  <si>
+    <t>stil</t>
+  </si>
+  <si>
+    <t>sgl</t>
+  </si>
+  <si>
+    <t>Dlic2</t>
+  </si>
+  <si>
+    <t>dpld</t>
+  </si>
+  <si>
+    <t>fs(1)K10</t>
+  </si>
+  <si>
+    <t>CG12301</t>
+  </si>
+  <si>
+    <t>rdo</t>
+  </si>
+  <si>
+    <t>tutl</t>
+  </si>
+  <si>
+    <t>rhea</t>
+  </si>
+  <si>
+    <t>dos</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>MED4</t>
+  </si>
+  <si>
+    <t>fd59A</t>
+  </si>
+  <si>
+    <t>tra2</t>
+  </si>
+  <si>
+    <t>Galpha73B</t>
+  </si>
+  <si>
+    <t>cathD</t>
+  </si>
+  <si>
+    <t>bnl</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>Sema-2a</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>Pk92B</t>
+  </si>
+  <si>
+    <t>cta</t>
+  </si>
+  <si>
+    <t>Tina-1</t>
+  </si>
+  <si>
+    <t>MED24</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>Dat</t>
+  </si>
+  <si>
+    <t>zfh2</t>
+  </si>
+  <si>
+    <t>Lcp65Ag1</t>
+  </si>
+  <si>
+    <t>tum</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>mib1</t>
+  </si>
+  <si>
+    <t>dpp</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>Idgf2</t>
+  </si>
+  <si>
+    <t>CG32486</t>
+  </si>
+  <si>
+    <t>alpha-Spec</t>
+  </si>
+  <si>
+    <t>bhr</t>
+  </si>
+  <si>
+    <t>elav</t>
+  </si>
+  <si>
+    <t>wupA</t>
+  </si>
+  <si>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>SelD</t>
+  </si>
+  <si>
+    <t>CkIIalpha</t>
+  </si>
+  <si>
+    <t>lmd</t>
   </si>
   <si>
     <t>dah</t>
   </si>
   <si>
-    <t>sqd</t>
-  </si>
-  <si>
-    <t>spin</t>
-  </si>
-  <si>
-    <t>dj</t>
-  </si>
-  <si>
-    <t>Nf1</t>
-  </si>
-  <si>
-    <t>slam</t>
-  </si>
-  <si>
-    <t>rdx</t>
-  </si>
-  <si>
-    <t>LCBP1</t>
-  </si>
-  <si>
-    <t>Dhc64C</t>
-  </si>
-  <si>
-    <t>Galpha73B</t>
+    <t>l(2)gd1</t>
   </si>
   <si>
     <t>flw</t>
   </si>
   <si>
-    <t>d</t>
+    <t>fw</t>
+  </si>
+  <si>
+    <t>CadN</t>
+  </si>
+  <si>
+    <t>CG2681</t>
+  </si>
+  <si>
+    <t>Dok</t>
+  </si>
+  <si>
+    <t>fog</t>
+  </si>
+  <si>
+    <t>Syx1A</t>
+  </si>
+  <si>
+    <t>sec23</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>SelG</t>
+  </si>
+  <si>
+    <t>cnc</t>
   </si>
   <si>
     <t>numb</t>
   </si>
   <si>
-    <t>sina</t>
-  </si>
-  <si>
-    <t>l(3)mbt</t>
-  </si>
-  <si>
-    <t>pn</t>
-  </si>
-  <si>
-    <t>bowl</t>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>foxo</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>Lac</t>
+  </si>
+  <si>
+    <t>chic</t>
+  </si>
+  <si>
+    <t>Sb</t>
+  </si>
+  <si>
+    <t>siz</t>
+  </si>
+  <si>
+    <t>disco</t>
+  </si>
+  <si>
+    <t>frc</t>
+  </si>
+  <si>
+    <t>th</t>
+  </si>
+  <si>
+    <t>sty</t>
+  </si>
+  <si>
+    <t>pnr</t>
+  </si>
+  <si>
+    <t>ofs</t>
+  </si>
+  <si>
+    <t>RpL30</t>
+  </si>
+  <si>
+    <t>E(z)</t>
+  </si>
+  <si>
+    <t>Dl</t>
+  </si>
+  <si>
+    <t>aft</t>
+  </si>
+  <si>
+    <t>trc</t>
+  </si>
+  <si>
+    <t>Pgant35A</t>
+  </si>
+  <si>
+    <t>Yp1</t>
+  </si>
+  <si>
+    <t>18w</t>
+  </si>
+  <si>
+    <t>Moe</t>
+  </si>
+  <si>
+    <t>fal</t>
+  </si>
+  <si>
+    <t>Hs6st</t>
+  </si>
+  <si>
+    <t>Sh</t>
+  </si>
+  <si>
+    <t>Pde8</t>
+  </si>
+  <si>
+    <t>meso18E</t>
+  </si>
+  <si>
+    <t>ken</t>
   </si>
   <si>
     <t>sdt</t>
   </si>
   <si>
-    <t>Abd-B</t>
-  </si>
-  <si>
-    <t>fs(2)ltoPP43</t>
-  </si>
-  <si>
-    <t>Pop2</t>
-  </si>
-  <si>
-    <t>Hem</t>
-  </si>
-  <si>
-    <t>mri</t>
-  </si>
-  <si>
-    <t>CG9520</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Cka</t>
+    <t>Es2</t>
+  </si>
+  <si>
+    <t>prod</t>
+  </si>
+  <si>
+    <t>brat</t>
+  </si>
+  <si>
+    <t>fs(1)M3</t>
+  </si>
+  <si>
+    <t>CG34417</t>
+  </si>
+  <si>
+    <t>ben</t>
+  </si>
+  <si>
+    <t>Glycogenin</t>
   </si>
   <si>
     <t>Eip74EF</t>
   </si>
   <si>
-    <t>wal</t>
-  </si>
-  <si>
-    <t>kuk</t>
-  </si>
-  <si>
-    <t>Su(var)2-10</t>
-  </si>
-  <si>
-    <t>Nrx-IV</t>
-  </si>
-  <si>
-    <t>fru</t>
-  </si>
-  <si>
-    <t>Myo31DF</t>
-  </si>
-  <si>
-    <t>Iswi</t>
-  </si>
-  <si>
-    <t>asf1</t>
-  </si>
-  <si>
-    <t>alien</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>fs(1)K10</t>
-  </si>
-  <si>
-    <t>wrapper</t>
-  </si>
-  <si>
-    <t>Tina-1</t>
-  </si>
-  <si>
-    <t>vap</t>
-  </si>
-  <si>
-    <t>Idgf5</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>lic</t>
-  </si>
-  <si>
-    <t>bun</t>
-  </si>
-  <si>
-    <t>Scgdelta</t>
-  </si>
-  <si>
-    <t>Ald</t>
-  </si>
-  <si>
-    <t>18w</t>
-  </si>
-  <si>
-    <t>esg</t>
-  </si>
-  <si>
-    <t>Arc42</t>
-  </si>
-  <si>
-    <t>Dscam</t>
-  </si>
-  <si>
-    <t>rux</t>
-  </si>
-  <si>
-    <t>hdc</t>
-  </si>
-  <si>
-    <t>SelD</t>
-  </si>
-  <si>
-    <t>Rbp9</t>
-  </si>
-  <si>
-    <t>CG12896</t>
-  </si>
-  <si>
-    <t>fred</t>
-  </si>
-  <si>
-    <t>wus</t>
-  </si>
-  <si>
-    <t>Ddx1</t>
-  </si>
-  <si>
-    <t>par-6</t>
-  </si>
-  <si>
-    <t>FKBP59</t>
-  </si>
-  <si>
-    <t>opa</t>
-  </si>
-  <si>
-    <t>dsx</t>
-  </si>
-  <si>
-    <t>Idgf1</t>
-  </si>
-  <si>
-    <t>gro</t>
-  </si>
-  <si>
-    <t>lva</t>
-  </si>
-  <si>
-    <t>Cp1</t>
-  </si>
-  <si>
-    <t>ofs</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>Mtl</t>
-  </si>
-  <si>
-    <t>Oseg1</t>
-  </si>
-  <si>
-    <t>mth</t>
-  </si>
-  <si>
-    <t>sec13</t>
-  </si>
-  <si>
-    <t>sn</t>
-  </si>
-  <si>
-    <t>drk</t>
-  </si>
-  <si>
-    <t>Nrt</t>
-  </si>
-  <si>
-    <t>CG14995</t>
-  </si>
-  <si>
-    <t>rdo</t>
-  </si>
-  <si>
-    <t>CycE</t>
-  </si>
-  <si>
-    <t>CG32082</t>
-  </si>
-  <si>
-    <t>mfas</t>
-  </si>
-  <si>
-    <t>tra2</t>
-  </si>
-  <si>
-    <t>puc</t>
-  </si>
-  <si>
-    <t>ct</t>
-  </si>
-  <si>
-    <t>xmas-2</t>
-  </si>
-  <si>
-    <t>capu</t>
-  </si>
-  <si>
-    <t>twi</t>
-  </si>
-  <si>
-    <t>Pvr</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>dco</t>
-  </si>
-  <si>
-    <t>bt</t>
-  </si>
-  <si>
-    <t>Sb</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>knrl</t>
-  </si>
-  <si>
-    <t>Jafrac2</t>
-  </si>
-  <si>
-    <t>Dap160</t>
-  </si>
-  <si>
-    <t>prd</t>
-  </si>
-  <si>
-    <t>sll</t>
-  </si>
-  <si>
-    <t>rad50</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>dl</t>
-  </si>
-  <si>
-    <t>Mmp1</t>
-  </si>
-  <si>
-    <t>cathD</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>Apc</t>
-  </si>
-  <si>
-    <t>sktl</t>
-  </si>
-  <si>
-    <t>Cks30A</t>
+    <t>Antp</t>
   </si>
   <si>
     <t>PebIII</t>
   </si>
   <si>
-    <t>cta</t>
-  </si>
-  <si>
-    <t>CG12301</t>
-  </si>
-  <si>
-    <t>CG34417</t>
-  </si>
-  <si>
-    <t>Snap</t>
-  </si>
-  <si>
-    <t>chinmo</t>
-  </si>
-  <si>
-    <t>gkt</t>
-  </si>
-  <si>
-    <t>MYPT-75D</t>
-  </si>
-  <si>
-    <t>Cyt-c-d</t>
-  </si>
-  <si>
-    <t>LanB1</t>
-  </si>
-  <si>
-    <t>toe</t>
-  </si>
-  <si>
-    <t>Chc</t>
-  </si>
-  <si>
-    <t>CG17221</t>
-  </si>
-  <si>
-    <t>Fmr1</t>
+    <t>blow</t>
   </si>
   <si>
     <t>trio</t>
   </si>
   <si>
-    <t>l(2)37Cc</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>Khc</t>
-  </si>
-  <si>
-    <t>CG9445</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>sls</t>
-  </si>
-  <si>
-    <t>Gtp-bp</t>
-  </si>
-  <si>
-    <t>snf</t>
-  </si>
-  <si>
-    <t>Pvf1</t>
-  </si>
-  <si>
-    <t>emp</t>
-  </si>
-  <si>
-    <t>peb</t>
-  </si>
-  <si>
-    <t>CkIIalpha</t>
-  </si>
-  <si>
-    <t>dib</t>
-  </si>
-  <si>
-    <t>siz</t>
-  </si>
-  <si>
-    <t>Mef2</t>
-  </si>
-  <si>
-    <t>Dcp-1</t>
-  </si>
-  <si>
-    <t>dpld</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>poe</t>
-  </si>
-  <si>
-    <t>trc</t>
-  </si>
-  <si>
-    <t>dock</t>
-  </si>
-  <si>
-    <t>Pk92B</t>
-  </si>
-  <si>
-    <t>ics</t>
-  </si>
-  <si>
-    <t>ash1</t>
-  </si>
-  <si>
-    <t>Hr46</t>
-  </si>
-  <si>
-    <t>mbo</t>
-  </si>
-  <si>
-    <t>scrib</t>
-  </si>
-  <si>
-    <t>beta4GalNAcTA</t>
-  </si>
-  <si>
-    <t>Ice</t>
-  </si>
-  <si>
-    <t>amx</t>
-  </si>
-  <si>
-    <t>Rab7</t>
-  </si>
-  <si>
-    <t>tow</t>
-  </si>
-  <si>
-    <t>Ca-alpha1D</t>
-  </si>
-  <si>
-    <t>chif</t>
-  </si>
-  <si>
-    <t>Rheb</t>
-  </si>
-  <si>
-    <t>stil</t>
-  </si>
-  <si>
-    <t>tutl</t>
-  </si>
-  <si>
-    <t>emb</t>
-  </si>
-  <si>
-    <t>CG4500</t>
-  </si>
-  <si>
-    <t>inaC</t>
-  </si>
-  <si>
-    <t>car</t>
-  </si>
-  <si>
-    <t>tld</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>Atpalpha</t>
-  </si>
-  <si>
-    <t>jumu</t>
-  </si>
-  <si>
-    <t>esc</t>
-  </si>
-  <si>
-    <t>E(bx)</t>
-  </si>
-  <si>
-    <t>ry</t>
-  </si>
-  <si>
-    <t>Idgf2</t>
-  </si>
-  <si>
-    <t>Vhl</t>
-  </si>
-  <si>
-    <t>G-salpha60A</t>
-  </si>
-  <si>
-    <t>Tab2</t>
-  </si>
-  <si>
-    <t>spn-A</t>
-  </si>
-  <si>
-    <t>pcm</t>
-  </si>
-  <si>
-    <t>NetB</t>
-  </si>
-  <si>
-    <t>Jra</t>
-  </si>
-  <si>
-    <t>tra</t>
+    <t>caup</t>
+  </si>
+  <si>
+    <t>eya</t>
+  </si>
+  <si>
+    <t>Su(z)12</t>
+  </si>
+  <si>
+    <t>lin</t>
+  </si>
+  <si>
+    <t>Alh</t>
   </si>
   <si>
     <t>Dredd</t>
-  </si>
-  <si>
-    <t>kkv</t>
-  </si>
-  <si>
-    <t>dpn</t>
-  </si>
-  <si>
-    <t>CdsA</t>
-  </si>
-  <si>
-    <t>ftz-f1</t>
-  </si>
-  <si>
-    <t>morgue</t>
-  </si>
-  <si>
-    <t>Rho1</t>
-  </si>
-  <si>
-    <t>inv</t>
-  </si>
-  <si>
-    <t>scyl</t>
-  </si>
-  <si>
-    <t>Borr</t>
-  </si>
-  <si>
-    <t>shrb</t>
-  </si>
-  <si>
-    <t>qm</t>
-  </si>
-  <si>
-    <t>RhoGAPp190</t>
-  </si>
-  <si>
-    <t>Hs2st</t>
-  </si>
-  <si>
-    <t>btl</t>
-  </si>
-  <si>
-    <t>cbt</t>
-  </si>
-  <si>
-    <t>mbl</t>
-  </si>
-  <si>
-    <t>ninaE</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>CG34379</t>
-  </si>
-  <si>
-    <t>ap</t>
-  </si>
-  <si>
-    <t>crc</t>
-  </si>
-  <si>
-    <t>bap</t>
-  </si>
-  <si>
-    <t>svr</t>
-  </si>
-  <si>
-    <t>ytr</t>
-  </si>
-  <si>
-    <t>fl(2)d</t>
-  </si>
-  <si>
-    <t>E2f</t>
-  </si>
-  <si>
-    <t>zfh2</t>
-  </si>
-  <si>
-    <t>Mkp3</t>
-  </si>
-  <si>
-    <t>dsf</t>
-  </si>
-  <si>
-    <t>mmy</t>
-  </si>
-  <si>
-    <t>Eip71CD</t>
-  </si>
-  <si>
-    <t>msk</t>
-  </si>
-  <si>
-    <t>disco</t>
-  </si>
-  <si>
-    <t>Lim1</t>
-  </si>
-  <si>
-    <t>Atg5</t>
-  </si>
-  <si>
-    <t>Ggamma1</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
-    <t>Patj</t>
-  </si>
-  <si>
-    <t>dmt</t>
-  </si>
-  <si>
-    <t>Akt1</t>
-  </si>
-  <si>
-    <t>Rack1</t>
-  </si>
-  <si>
-    <t>ix</t>
-  </si>
-  <si>
-    <t>noc</t>
-  </si>
-  <si>
-    <t>Pcaf</t>
-  </si>
-  <si>
-    <t>loco</t>
-  </si>
-  <si>
-    <t>Caf1</t>
-  </si>
-  <si>
-    <t>ena</t>
-  </si>
-  <si>
-    <t>CtBP</t>
-  </si>
-  <si>
-    <t>CG6416</t>
-  </si>
-  <si>
-    <t>CG9509</t>
-  </si>
-  <si>
-    <t>shot</t>
-  </si>
-  <si>
-    <t>emc</t>
-  </si>
-  <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>E(z)</t>
-  </si>
-  <si>
-    <t>EcR</t>
-  </si>
-  <si>
-    <t>sns</t>
-  </si>
-  <si>
-    <t>frc</t>
-  </si>
-  <si>
-    <t>Not1</t>
-  </si>
-  <si>
-    <t>glu</t>
-  </si>
-  <si>
-    <t>betaTub56D</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>ksr</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>drm</t>
-  </si>
-  <si>
-    <t>Syx1A</t>
-  </si>
-  <si>
-    <t>pyd</t>
-  </si>
-  <si>
-    <t>Pak</t>
-  </si>
-  <si>
-    <t>fal</t>
-  </si>
-  <si>
-    <t>Fas3</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>Prm</t>
-  </si>
-  <si>
-    <t>Mer</t>
-  </si>
-  <si>
-    <t>Mlc1</t>
-  </si>
-  <si>
-    <t>CG3987</t>
-  </si>
-  <si>
-    <t>E2f2</t>
-  </si>
-  <si>
-    <t>her</t>
-  </si>
-  <si>
-    <t>th</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>qua</t>
-  </si>
-  <si>
-    <t>wls</t>
-  </si>
-  <si>
-    <t>dome</t>
-  </si>
-  <si>
-    <t>RpL30</t>
-  </si>
-  <si>
-    <t>cas</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>CadN</t>
-  </si>
-  <si>
-    <t>Mmp2</t>
-  </si>
-  <si>
-    <t>dom</t>
-  </si>
-  <si>
-    <t>tok</t>
-  </si>
-  <si>
-    <t>fw</t>
-  </si>
-  <si>
-    <t>Crk</t>
-  </si>
-  <si>
-    <t>CG17739</t>
-  </si>
-  <si>
-    <t>Idgf4</t>
-  </si>
-  <si>
-    <t>bs</t>
-  </si>
-  <si>
-    <t>tsh</t>
-  </si>
-  <si>
-    <t>ImpE3</t>
-  </si>
-  <si>
-    <t>Lac</t>
-  </si>
-  <si>
-    <t>dup</t>
-  </si>
-  <si>
-    <t>cnk</t>
-  </si>
-  <si>
-    <t>ssh</t>
-  </si>
-  <si>
-    <t>Sxl</t>
-  </si>
-  <si>
-    <t>G-ialpha65A</t>
-  </si>
-  <si>
-    <t>kay</t>
-  </si>
-  <si>
-    <t>cher</t>
-  </si>
-  <si>
-    <t>eIF-4E</t>
-  </si>
-  <si>
-    <t>Lar</t>
-  </si>
-  <si>
-    <t>nej</t>
-  </si>
-  <si>
-    <t>pdm2</t>
-  </si>
-  <si>
-    <t>CSN4</t>
-  </si>
-  <si>
-    <t>SelG</t>
-  </si>
-  <si>
-    <t>foxo</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B225"/>
+  <dimension ref="A1:B231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1309,466 +1357,466 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B64" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1776,148 +1824,148 @@
         <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B72" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="B73" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="B78" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B80" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B81" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="B84" t="s">
         <v>145</v>
@@ -1925,15 +1973,15 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" t="s">
         <v>146</v>
-      </c>
-      <c r="B85" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="B86" t="s">
         <v>148</v>
@@ -1944,143 +1992,143 @@
         <v>149</v>
       </c>
       <c r="B87" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
+        <v>150</v>
+      </c>
+      <c r="B88" t="s">
         <v>151</v>
-      </c>
-      <c r="B88" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" t="s">
         <v>153</v>
-      </c>
-      <c r="B89" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
+        <v>154</v>
+      </c>
+      <c r="B90" t="s">
         <v>155</v>
-      </c>
-      <c r="B90" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
+        <v>156</v>
+      </c>
+      <c r="B91" t="s">
         <v>157</v>
-      </c>
-      <c r="B91" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B93" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B95" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="B96" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B97" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B98" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B100" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B101" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="B102" t="s">
-        <v>174</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="B104" t="s">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2088,31 +2136,31 @@
         <v>177</v>
       </c>
       <c r="B105" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="B106" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="B107" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>104</v>
+      </c>
+      <c r="B108" t="s">
         <v>181</v>
-      </c>
-      <c r="B108" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2125,34 +2173,34 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="B110" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B111" t="s">
-        <v>185</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="B112" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="B113" t="s">
-        <v>187</v>
+        <v>94</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2160,7 +2208,7 @@
         <v>188</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2168,12 +2216,12 @@
         <v>189</v>
       </c>
       <c r="B115" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="B116" t="s">
         <v>190</v>
@@ -2184,871 +2232,919 @@
         <v>191</v>
       </c>
       <c r="B117" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="B118" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>193</v>
+        <v>64</v>
       </c>
       <c r="B119" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="B120" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>195</v>
+      </c>
+      <c r="B121" t="s">
         <v>196</v>
-      </c>
-      <c r="B121" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>197</v>
+        <v>32</v>
       </c>
       <c r="B122" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B123" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B124" t="s">
-        <v>200</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="B127" t="s">
-        <v>99</v>
+        <v>200</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="B128" t="s">
-        <v>19</v>
+        <v>202</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="B129" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="B130" t="s">
-        <v>207</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B131" t="s">
-        <v>190</v>
+        <v>71</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="B132" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="B133" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B134" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="B136" t="s">
-        <v>212</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B137" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>211</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="B139" t="s">
-        <v>215</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B140" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>218</v>
+        <v>145</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B142" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B143" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>222</v>
+        <v>66</v>
       </c>
       <c r="B144" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>224</v>
+        <v>164</v>
       </c>
       <c r="B145" t="s">
-        <v>62</v>
+        <v>216</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>75</v>
+        <v>217</v>
       </c>
       <c r="B146" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B147" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="B148" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="B149" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="B150" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B151" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="B152" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B153" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="B154" t="s">
-        <v>232</v>
+        <v>46</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B155" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="B156" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>226</v>
+        <v>140</v>
       </c>
       <c r="B157" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B158" t="s">
-        <v>202</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B159" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>237</v>
+        <v>26</v>
       </c>
       <c r="B160" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B161" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B162" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B163" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="B164" t="s">
-        <v>4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B165" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="B166" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="B167" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B168" t="s">
-        <v>132</v>
+        <v>246</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B169" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B170" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>132</v>
+        <v>251</v>
       </c>
       <c r="B171" t="s">
-        <v>89</v>
+        <v>252</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B172" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="B173" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B174" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B175" t="s">
-        <v>252</v>
+        <v>187</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>177</v>
+        <v>259</v>
       </c>
       <c r="B176" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B177" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>255</v>
+        <v>30</v>
       </c>
       <c r="B178" t="s">
-        <v>33</v>
+        <v>262</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B179" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="B180" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="B181" t="s">
-        <v>112</v>
+        <v>265</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="B182" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="B183" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>259</v>
+        <v>76</v>
       </c>
       <c r="B184" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>166</v>
+        <v>269</v>
       </c>
       <c r="B185" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B186" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B187" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>264</v>
+        <v>106</v>
       </c>
       <c r="B188" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>266</v>
+        <v>26</v>
       </c>
       <c r="B189" t="s">
-        <v>267</v>
+        <v>13</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B191" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="B192" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>66</v>
+        <v>278</v>
       </c>
       <c r="B193" t="s">
-        <v>272</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
       <c r="B194" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>225</v>
+        <v>19</v>
       </c>
       <c r="B195" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B196" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B197" t="s">
-        <v>35</v>
+        <v>285</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>110</v>
+        <v>286</v>
       </c>
       <c r="B198" t="s">
-        <v>3</v>
+        <v>287</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>106</v>
+        <v>288</v>
       </c>
       <c r="B199" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B200" t="s">
-        <v>280</v>
+        <v>210</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B201" t="s">
-        <v>187</v>
+        <v>290</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>28</v>
+        <v>291</v>
       </c>
       <c r="B202" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="B203" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>282</v>
+        <v>221</v>
       </c>
       <c r="B204" t="s">
-        <v>283</v>
+        <v>245</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>213</v>
+        <v>25</v>
       </c>
       <c r="B205" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>246</v>
+        <v>53</v>
       </c>
       <c r="B206" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>198</v>
+        <v>97</v>
       </c>
       <c r="B207" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B208" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="B210" t="s">
-        <v>229</v>
+        <v>72</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>154</v>
+        <v>297</v>
       </c>
       <c r="B211" t="s">
-        <v>288</v>
+        <v>190</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="B212" t="s">
-        <v>119</v>
+        <v>249</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="B213" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B214" t="s">
-        <v>282</v>
+        <v>251</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="B215" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="B216" t="s">
-        <v>209</v>
+        <v>302</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="B217" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>57</v>
+        <v>262</v>
       </c>
       <c r="B218" t="s">
-        <v>160</v>
+        <v>304</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B219" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>294</v>
+        <v>213</v>
       </c>
       <c r="B220" t="s">
-        <v>295</v>
+        <v>100</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>296</v>
+        <v>147</v>
       </c>
       <c r="B221" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="B222" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>221</v>
+        <v>286</v>
       </c>
       <c r="B223" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>299</v>
+        <v>166</v>
       </c>
       <c r="B224" t="s">
-        <v>208</v>
+        <v>310</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>66</v>
+        <v>241</v>
       </c>
       <c r="B225" t="s">
-        <v>300</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>141</v>
+      </c>
+      <c r="B226" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
+        <v>238</v>
+      </c>
+      <c r="B227" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" t="s">
+        <v>186</v>
+      </c>
+      <c r="B228" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>313</v>
+      </c>
+      <c r="B229" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>314</v>
+      </c>
+      <c r="B230" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>131</v>
+      </c>
+      <c r="B231" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
